--- a/test/quality_check/actual_output.xlsx
+++ b/test/quality_check/actual_output.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Program\VScode\workspace\data-governance\test\quality_check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20317F9-3922-4104-AA58-5CFE72575F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0C321C-0B83-4039-A6AE-C1A44E9BC225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8789" uniqueCount="2761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8789" uniqueCount="2764">
   <si>
     <t>上游信息</t>
   </si>
@@ -8365,6 +8365,19 @@
   <si>
     <t>1. 因为字段名为“最后维护部门名称”，业务定义是标识某个客户信息最新的修改部门，强调的是部门的“名称”这一说明描述类信息，而非具有特定编码规则的部门代码。虽然部门通常可能有对应的编码，但此处明确存储的是部门名称，属于说明描述类信息，应属于文本类，而非编码类。，当前字段所属类型可能错误，应为文本类，请联系业务确认
 2. 数据示例存在问题：字段所属类型为编码类，应存储具有编码规则的值，但数据示例'总行'是部门名称而非编码，与字段类型语义不匹配。</t>
+  </si>
+  <si>
+    <t>1. 数据示例'2029-01-01 00:00:00'不符合域类型'DATE'的限制: DATE应为8位日期数字（YYYYMMDD），实际14位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 数据示例'2026/4/19 6:34:44'不符合域类型'datetime'的限制: DATETIME应为14位日期时间数字（YYYYMMDDHHmmss），实际12位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. '是否枚举'为'否'但枚举值不为空
+2. 枚举值缺少代码，应填写'代码-码值'形式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8527,7 +8540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -8628,6 +8641,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12077,33 +12096,33 @@
         <v>55</v>
       </c>
     </row>
-    <row r="108" spans="10:29" ht="15" customHeight="1">
-      <c r="J108" s="2" t="s">
+    <row r="108" spans="10:29" s="34" customFormat="1" ht="15" customHeight="1">
+      <c r="J108" s="38" t="s">
         <v>337</v>
       </c>
-      <c r="O108" s="2" t="s">
+      <c r="O108" s="38" t="s">
         <v>351</v>
       </c>
-      <c r="P108" s="2" t="s">
+      <c r="P108" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="Q108" s="7">
+      <c r="Q108" s="39">
         <v>47119</v>
       </c>
-      <c r="R108" s="2" t="s">
+      <c r="R108" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="V108" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y108" s="2" t="s">
+      <c r="V108" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y108" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="AA108" t="s">
+      <c r="AA108" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="AB108" t="s">
-        <v>353</v>
+      <c r="AB108" s="34" t="s">
+        <v>2761</v>
       </c>
     </row>
     <row r="109" spans="10:29" ht="30" customHeight="1">
@@ -12738,7 +12757,7 @@
         <v>38</v>
       </c>
       <c r="AB131" t="s">
-        <v>424</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="132" spans="10:28" ht="15" customHeight="1">
@@ -13250,8 +13269,8 @@
       <c r="AA148" t="s">
         <v>38</v>
       </c>
-      <c r="AB148" t="s">
-        <v>479</v>
+      <c r="AB148" s="3" t="s">
+        <v>2763</v>
       </c>
     </row>
     <row r="149" spans="10:29" ht="30" customHeight="1">
